--- a/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
+++ b/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:33:49+00:00</t>
+    <t>2026-04-29T13:16:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
+++ b/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T13:16:27+00:00</t>
+    <t>2026-04-29T15:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
+++ b/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:13+00:00</t>
+    <t>2026-04-29T15:21:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
+++ b/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:33+00:00</t>
+    <t>2026-07-23T07:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
+++ b/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:54:45+00:00</t>
+    <t>2026-07-23T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
+++ b/main/ig/ValueSet-ror-questionnaire-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:00:07+00:00</t>
+    <t>2026-07-23T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
